--- a/teacher_forms/003_student_peer_evaluation_form--teacher_forms.xlsx
+++ b/teacher_forms/003_student_peer_evaluation_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -830,8 +830,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,12 +859,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'unable_to_determine'}</t>
+          <t>unable_to_determine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Unable to determine'}</t>
+          <t>Unable to determine</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_6,_'label':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 6, 'label': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_7,_'label':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 7, 'label': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_8,_'label':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 8, 'label': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_9,_'label':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 9, 'label': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_10,_'label':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 10, 'label': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
